--- a/projects/RPE1.xlsx
+++ b/projects/RPE1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpy/Work/cnio/dev/nf-repairome/RPE1/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpy/Work/cnio/dev/nf-repairome/projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F311EF-EF4D-5E46-B00F-6153B18AC244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3602E0-11A9-6141-98D2-EE13385BDA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8020" yWindow="2940" windowWidth="15760" windowHeight="9560" xr2:uid="{DFCB6EE1-989D-8A4A-A86D-07A95CBED23B}"/>
+    <workbookView xWindow="9600" yWindow="4160" windowWidth="15760" windowHeight="9560" xr2:uid="{DFCB6EE1-989D-8A4A-A86D-07A95CBED23B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>CELL</t>
   </si>
@@ -66,13 +66,31 @@
   </si>
   <si>
     <t>SRR29304327</t>
+  </si>
+  <si>
+    <t>SRR29304326</t>
+  </si>
+  <si>
+    <t>SRR29304325</t>
+  </si>
+  <si>
+    <t>SRR29304324</t>
+  </si>
+  <si>
+    <t>SRR29304323</t>
+  </si>
+  <si>
+    <t>Cut2</t>
+  </si>
+  <si>
+    <t>Cut3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -90,6 +108,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -453,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0EAC9F5-27FE-BE4A-A61A-85642E8C2168}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
@@ -501,7 +525,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>